--- a/AAII_Financials/Quarterly/UL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="92">
   <si>
     <t>UL</t>
   </si>
@@ -656,281 +656,295 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
-        <v>17690500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>16281300</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3">
+        <v>14636700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14771700</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
+        <v>14977100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>13784000</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>16670400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16785500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>16124700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>15440300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>16609200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16529800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>16271200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>32013600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>14996200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>28918500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14584400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>27774300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>13043000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>25530200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>26688600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>12911500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>29191800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>15472900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>32004100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>14606200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>29462400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>13877100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>28934500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>13859000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>29160500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>14772100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>31107200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>15634000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>31023800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>15705600</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -958,27 +972,27 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>19027900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>18220300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>19186700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1042,56 +1056,62 @@
       <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>17690500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>16281300</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3">
+        <v>14636700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14771700</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>14977100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>13784000</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>16670400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>16785500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-2903200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-2780000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>16609200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>16529800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-2915500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1155,8 +1175,14 @@
       <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1196,8 +1222,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1225,27 +1253,27 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>524500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>502200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>485200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1309,8 +1337,14 @@
       <c r="AM12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1422,110 +1456,116 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>207900</v>
-      </c>
-      <c r="G14" s="3">
-        <v>191300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>195400</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>254300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>234000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>167700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>168800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>331000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>317000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-99900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-99400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-848600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>629000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>605400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>484600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>666600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>405800</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-35500</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-145900</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>428600</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1535,56 +1575,62 @@
       <c r="AM14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>353600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>356900</v>
+      </c>
+      <c r="F15" s="3">
         <v>302300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>302100</v>
       </c>
-      <c r="F15" s="3">
-        <v>466800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>429600</v>
-      </c>
       <c r="H15" s="3">
+        <v>354700</v>
+      </c>
+      <c r="I15" s="3">
+        <v>326400</v>
+      </c>
+      <c r="J15" s="3">
         <v>124200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>133800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>425400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>428300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>131000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>125400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>411000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>409100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>121300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1694,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1686,234 +1738,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3">
-        <v>14356400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>13212800</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3">
+        <v>11658900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11766400</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>11923100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10973300</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>13384200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13476600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13447000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12876300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>13729800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13664200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13829200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>27191500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>24327900</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>23039200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>21824700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>21817700</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>24537600</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>26347100</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>19615300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>23961700</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>25089900</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>25668900</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
         <v>26314500</v>
       </c>
-      <c r="AM17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3334100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>3068500</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3">
+        <v>2977800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3005300</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3054000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2810700</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>3286200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3308900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2677700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2564000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2879400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2865600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2442000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4822100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>4590600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>4735100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>3705500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4870900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>4654200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5657000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>9847100</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>4972800</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4070600</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>5438300</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="3">
         <v>4709300</v>
       </c>
-      <c r="AM18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1953,282 +2019,296 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>-85700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-78900</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-73900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-74400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-82900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-79400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-64400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-64100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-111300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-47700</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-30200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-170500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-166100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-211100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-323400</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-240400</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-219600</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-120100</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-241200</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-212500</v>
       </c>
-      <c r="AM20" s="3" t="s">
+      <c r="AO20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3411400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3442900</v>
+      </c>
+      <c r="F21" s="3">
         <v>302300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>302100</v>
       </c>
-      <c r="F21" s="3">
-        <v>3886700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>3577100</v>
-      </c>
       <c r="H21" s="3">
+        <v>3494400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3216100</v>
+      </c>
+      <c r="J21" s="3">
         <v>124200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>133800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3785500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3811600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2891600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2768800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3354800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3338800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2607100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>6455800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>5595000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>5729200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6680900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6515700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>10788500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6101600</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>4820100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>6053100</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5416000</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
-        <v>326500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300500</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3">
+        <v>317600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>320500</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>293600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>270200</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>326800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>329100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>308400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>295300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>282200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>280900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>232400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -2292,234 +2372,252 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2990600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2752400</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3">
+        <v>2661400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2685900</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2686400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2472400</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>2981900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3002500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2250500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2155000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2875000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2861300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3194400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4710800</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>4542900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>4705000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>3535000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>4704800</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>4443000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>5333600</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>9606700</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>4753200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>3950500</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="3">
         <v>5197100</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN23" s="3">
         <v>4496900</v>
       </c>
-      <c r="AM23" s="3" t="s">
+      <c r="AO23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>752800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>692800</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3">
+        <v>781400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>788700</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>683500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>629100</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>830400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>836100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>449900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>430800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>756000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>752400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>494300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1235200</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>1044900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>1046700</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>951400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1028600</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>1262300</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>1402600</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1726100</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1176000</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>1043500</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="3">
         <v>1475400</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN24" s="3">
         <v>1166800</v>
       </c>
-      <c r="AM24" s="3" t="s">
+      <c r="AO24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2631,234 +2729,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2237800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>2059600</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3">
+        <v>1879900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1897300</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2002900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1843400</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>2151500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2166400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1800600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1724200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2119000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2108900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2700100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3475500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>3498000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>3658200</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>2583600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3676200</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>3180700</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>3931000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>7880600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>3577300</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>2907100</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>3721600</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" s="3">
         <v>3330100</v>
       </c>
-      <c r="AM26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="D27" s="3">
+        <v>1894200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1911700</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
         <v>2062200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1898000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>1982700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1996400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1624300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1555400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1936700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1927400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2531300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3139400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>3176900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>3361000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>2344800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3408500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>2957100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>3682300</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>7616200</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3359900</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>2653500</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>3489400</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="3">
         <v>3136400</v>
       </c>
-      <c r="AM27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2970,16 +3086,22 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>164500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2988,10 +3110,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>234900</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>216200</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -3035,14 +3157,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -3054,26 +3176,26 @@
         <v>5</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-34700</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-31800</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>648500</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3083,8 +3205,14 @@
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3196,8 +3324,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3309,234 +3443,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>80700</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
         <v>85700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>78900</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>73900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>74400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>82900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>79400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>64400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>64100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>43800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>111300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>47700</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>30200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>170500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>166100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>211100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>323400</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>240400</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>219600</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>120100</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="3">
         <v>241200</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN32" s="3">
         <v>212500</v>
       </c>
-      <c r="AM32" s="3" t="s">
+      <c r="AO32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="D33" s="3">
+        <v>1894200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1911700</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
         <v>2062200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1898000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>1982700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1996400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1624300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1555400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1936700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1927400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2531300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3139400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>3176900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>3361000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>2344800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3408500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>2957100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>3682300</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>7581500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3328000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>3302000</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>3489400</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="3">
         <v>3136400</v>
       </c>
-      <c r="AM33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3648,239 +3800,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="D35" s="3">
+        <v>1894200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1911700</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
         <v>2062200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1898000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>1982700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1996400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1624300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1555400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1936700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1927400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2531300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3139400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>3176900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>3361000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>2344800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3408500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>2957100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>3682300</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>7581500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3328000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>3302000</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>3489400</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" s="3">
         <v>3136400</v>
       </c>
-      <c r="AM35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3920,8 +4090,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3961,1025 +4133,1081 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5399300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5449100</v>
+      </c>
+      <c r="F41" s="3">
         <v>4627200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4624000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5101600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4695200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6352600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6843600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5325200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5362000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4597100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4402000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5452000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5425900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4623300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>5263300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>4427700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>4059200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>4725300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4790900</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>3863700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4382100</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>3721600</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="3">
         <v>5627900</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN41" s="3">
         <v>3969800</v>
       </c>
-      <c r="AM41" s="3" t="s">
+      <c r="AO41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1390400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1403200</v>
+      </c>
+      <c r="F42" s="3">
         <v>1257500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1256600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1204900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1108900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1223700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1318300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1542900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1553600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1872400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1793000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1462900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1455900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1359400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>1192500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>959600</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>947600</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>1024100</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>1045500</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>950900</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>863900</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>925600</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="3">
         <v>703100</v>
       </c>
-      <c r="AM42" s="3" t="s">
+      <c r="AO42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11957000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12067300</v>
+      </c>
+      <c r="F43" s="3">
         <v>6744200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6739400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>9418700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8668400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5364900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5779600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8671400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8731300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5561000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5324900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8979300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>8936300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>6068200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>7904200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>7503300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>8660200</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>8007600</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>10221300</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>8318400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>8040700</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>6406600</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL43" s="3">
         <v>7341200</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN43" s="3">
         <v>6360900</v>
       </c>
-      <c r="AM43" s="3" t="s">
+      <c r="AO43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5166200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5213900</v>
+      </c>
+      <c r="F44" s="3">
         <v>4747000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>4743600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6461500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5946800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5359800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5774000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6022700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6064300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5658200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5418100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6187800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6158200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>6338600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>5036700</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>4405500</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>4553300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>4701600</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>5374000</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>5144900</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>4662100</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>4445300</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="3">
         <v>4669700</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN44" s="3">
         <v>5021600</v>
       </c>
-      <c r="AM44" s="3" t="s">
+      <c r="AO44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>523200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>528100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1054400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1053600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>350000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>322100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1046700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1127600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>103900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>104600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1528700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1463800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>140800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>140200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1048400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>60700</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>86800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>35300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>92600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>41600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>142300</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>3737600</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>3617300</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL45" s="3">
         <v>58300</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN45" s="3">
         <v>241800</v>
       </c>
-      <c r="AM45" s="3" t="s">
+      <c r="AO45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24436200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>24661600</v>
+      </c>
+      <c r="F46" s="3">
         <v>20037600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>20023500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22536700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20741500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19871600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>21407500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21666100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21815700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19787800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>18947900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>22222700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22116500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20473400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>19457400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>17382900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>18255600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>18551100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>21546300</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>18514800</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>21773300</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>19054800</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL46" s="3">
         <v>18622800</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN46" s="3">
         <v>16297200</v>
       </c>
-      <c r="AM46" s="3" t="s">
+      <c r="AO46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3566800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3599700</v>
+      </c>
+      <c r="F47" s="3">
         <v>3494200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3491700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1639500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1508900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1489800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1605000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1386500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1396100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1348500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1291300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1083000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1077800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1068700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>883500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>924700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>731700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>986800</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>863600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>768000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>704900</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>757300</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>768600</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="3">
         <v>790000</v>
       </c>
-      <c r="AM47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10688900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10787500</v>
+      </c>
+      <c r="F48" s="3">
         <v>10557700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>10550300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>12847900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>11824500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12081000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13014700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11891100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>11973200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>11834900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11332600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11561100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>11505900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>11510100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>12330600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>12761600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>12524300</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>13619200</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>14782000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>14459700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>13078300</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>11681000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>12412600</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN48" s="3">
         <v>13701900</v>
       </c>
-      <c r="AM48" s="3" t="s">
+      <c r="AO48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41214400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>41594600</v>
+      </c>
+      <c r="F49" s="3">
         <v>40817200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>40788500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>44675300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>41116500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>42345000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>45617900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>44038400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>44342400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>43623300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>41771800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>43627700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>43419200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>43271300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>38728400</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>32828700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>31390200</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>35034800</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>37048600</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>35279500</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>31510400</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>31865600</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>29682200</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>32201100</v>
       </c>
-      <c r="AM49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5091,8 +5319,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5204,121 +5438,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6750800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6813100</v>
+      </c>
+      <c r="F52" s="3">
         <v>6134800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6130500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6250100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>5752300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5096800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5490700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5424800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>5462300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4934200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4724800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5921400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>5893100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>5168300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>4896900</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>4666800</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>4072700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>4980500</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>4806900</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>4079000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>4255800</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>4280400</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>3594900</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>3246800</v>
       </c>
-      <c r="AM52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5430,121 +5676,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87893300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>88704000</v>
+      </c>
+      <c r="F54" s="3">
         <v>82741600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>82683300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>89253100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>82143300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>82565500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>88947100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>85537300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>86128000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>83194400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>79663400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>85599300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>85190100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>83168800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>76296800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>68564700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>66974600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>73172500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>79047400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>73101000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>71322800</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>67639200</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL54" s="3">
         <v>65081000</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN54" s="3">
         <v>66236900</v>
       </c>
-      <c r="AM54" s="3" t="s">
+      <c r="AO54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5584,8 +5842,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5625,217 +5885,225 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21987900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>22190700</v>
+      </c>
+      <c r="F57" s="3">
         <v>12908300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12899200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>19071100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>17551900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10620100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11441000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>18386400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18513300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>11445800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>10960000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>18850400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>18760300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>11862800</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>15830000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>15624500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>14936400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>16674500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>17628800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>17293500</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>15129300</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>15063800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>14947200</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>16281900</v>
       </c>
-      <c r="AM57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9302000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>9387800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3031600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3029400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8402800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7733500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7233700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7792800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>8189200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>8245800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5622900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5384200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7330800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7295700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6171800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>5195000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>4963100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>5828800</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5296600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>6879500</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>4321900</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>12165800</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5851,460 +6119,490 @@
       <c r="AM58" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1717100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1733000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3372100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3369700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2002300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1842800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2465100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2655600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1421800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1431700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2758900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2641800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1774000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1765500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2879100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>1715000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>1607100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1803900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1715100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2129000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2488100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1689800</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>10940500</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>7290700</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>7846900</v>
       </c>
-      <c r="AM59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33007000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>33311400</v>
+      </c>
+      <c r="F60" s="3">
         <v>25433800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>25415900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>29476200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>27128200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>26124900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>28144100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>27997400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>28190700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>25983200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>24880400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>27955200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>27821600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>27174300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>22740100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>22194700</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>22569100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>23686300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>26637400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>24103400</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>28985000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>26004400</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL60" s="3">
         <v>22237800</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN60" s="3">
         <v>24128800</v>
       </c>
-      <c r="AM60" s="3" t="s">
+      <c r="AO60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27382600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>27635200</v>
+      </c>
+      <c r="F61" s="3">
         <v>30170200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>30149000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>29207300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>26880700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>25950900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27956700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>25727000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>25904600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>27119500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>25968500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>26193200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>26068000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>25342500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>26032500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>24932800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>24254700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>26608400</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>28626800</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>27662100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>22529900</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>18470200</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>16327200</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>13082100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1139000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1149500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>1149500</v>
+      </c>
+      <c r="G62" s="3">
         <v>1148700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1337600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1231100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1407000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1515700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1349000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1358300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1199300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1148400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1099300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1094100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>976800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>7767600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>6745800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>6247100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>7199100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>7373200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>6841100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>6498000</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>7022500</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>7646400</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>9094700</v>
       </c>
-      <c r="AM62" s="3" t="s">
+      <c r="AO62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6416,8 +6714,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6529,8 +6833,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6642,121 +6952,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66978200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>67596000</v>
+      </c>
+      <c r="F66" s="3">
         <v>62092300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>62048600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>65846200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>60601000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>59214200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>63791000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>60869000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>61289200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>60243200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>57686300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>61668100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>61373300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>59976500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>59342500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>54607600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>53782900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>58277400</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>63477800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>59467900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>58801200</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>52347600</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>46901400</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN66" s="3">
         <v>47040400</v>
       </c>
-      <c r="AM66" s="3" t="s">
+      <c r="AO66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6796,8 +7118,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6909,8 +7233,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7022,8 +7352,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7135,8 +7471,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7248,121 +7590,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>52474600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>52958600</v>
+      </c>
+      <c r="F72" s="3">
         <v>51930300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>51893700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>59542000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>54799000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>51476300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>55455100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>53109400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>53476100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>52008400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>49801000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>56638600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>56367900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>53706300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>16361200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>13371000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>12607400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>14269600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>14880000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>12923700</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>11847400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>14602700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>17489600</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN72" s="3">
         <v>18471100</v>
       </c>
-      <c r="AM72" s="3" t="s">
+      <c r="AO72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7474,8 +7828,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7587,8 +7947,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7700,121 +8066,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18501100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>18671700</v>
+      </c>
+      <c r="F76" s="3">
         <v>18234100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>18221300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20898400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>19233700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20695700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22295300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21759300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21909600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20008800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19159600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>21022900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20922400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20328100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>16954200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>13957100</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>13191700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>14895100</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>15569600</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>13633100</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>12521600</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>15291600</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="3">
         <v>18179600</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN76" s="3">
         <v>19196500</v>
       </c>
-      <c r="AM76" s="3" t="s">
+      <c r="AO76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7926,239 +8304,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="D81" s="3">
+        <v>1894200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1911700</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
         <v>2062200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1898000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>1982700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1996400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1624300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1555400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1936700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1927400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2531300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3139400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>3176900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>3361000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>2344800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3408500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>2957100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>3682300</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>7581500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3328000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>3302000</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>3489400</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN81" s="3">
         <v>3136400</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8198,121 +8594,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>354700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>326400</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
         <v>425400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>428300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>315900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>411000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>409100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>228700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>209800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>440100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>467700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>620400</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>1912900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2060000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1024400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2237900</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1182100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1181800</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1348300</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>869500</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>856100</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>919100</v>
       </c>
-      <c r="AM83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8424,8 +8828,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8537,8 +8947,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8650,8 +9066,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8763,8 +9185,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8876,121 +9304,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>1470400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1483900</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
         <v>1342900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1235900</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>1802200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1814700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3349200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3207000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1837300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1828600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2261900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>8649600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>9246400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>3661700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>9155900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>2930200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>5536000</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>2953600</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>5730000</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>2451500</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>6136700</v>
       </c>
-      <c r="AM89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9030,121 +9470,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-411600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-378800</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="D91" s="3">
+        <v>-303900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-306700</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-311800</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-287000</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-330500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-332800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-565900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-541900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-260900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-259700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-461200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-441000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-441000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-422000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-422000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-758000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-881000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-438000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1485900</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-683500</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-997600</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-543500</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-939100</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-754000</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-1226600</v>
       </c>
-      <c r="AM91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9256,8 +9704,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9369,121 +9823,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>-381600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-385100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
         <v>-380500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-350200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-210000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-211500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1157300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1108200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-109200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-108600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>1541600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3521900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-1511800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-603000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-2525800</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-877100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>7278900</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1582200</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-6080100</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-516100</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-2986200</v>
       </c>
-      <c r="AM94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9523,121 +9989,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>1161300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>1311800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1207300</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>1144300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1152200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1194300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1143600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1202000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1196200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>1150500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-4864100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-4368000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-2200300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-4752400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2548000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2431900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2232200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-2249600</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-2144100</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-2161000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9749,8 +10223,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9862,8 +10342,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9975,343 +10461,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>-675800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-682000</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1727000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1589400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1154000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1161900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2599800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2489400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1358600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1352100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-4256700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-7702400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-5924700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2167100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-5269500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1048600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-13341200</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-433700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-1762600</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>154800</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-2999100</v>
       </c>
-      <c r="AM100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>-223100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-205400</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
         <v>-4800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>-46000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-17500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-17400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-107400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-98500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>101400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>107800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>37000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>309200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-422600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-262600</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-202100</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-148200</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>79100</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>215400</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-225500</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>154900</v>
       </c>
-      <c r="AM101" s="3" t="s">
+      <c r="AO101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>457600</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>461800</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-987700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-909000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>433400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>436400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-456000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-436600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>352100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>350400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-560500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2265500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>1387300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>629000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>1158500</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>856300</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-862500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>704900</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-1897300</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>1864700</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>306400</v>
       </c>
-      <c r="AM102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
